--- a/data/excel/orangeHRM.xlsx
+++ b/data/excel/orangeHRM.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Handson\PlaywrightWithTypescript_WishInfiniteYoutube\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F37D801-B872-4479-ABCA-D4DE1BB1282F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ABD2A9-C155-4F2B-8F3D-5D3541F6BD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Employee" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -70,6 +71,63 @@
   </si>
   <si>
     <t>Validate Invalid Login Credentials</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Marital Status</t>
+  </si>
+  <si>
+    <t>EMP001</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>EMP002</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>EMP003</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>EMP004</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Jones</t>
   </si>
 </sst>
 </file>
@@ -128,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -137,6 +195,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,4 +548,104 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD44BA9-39B8-4A65-8659-551042417F2F}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="6">
+        <v>29351</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6">
+        <v>34931</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="6">
+        <v>25614</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6">
+        <v>31354</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>